--- a/2-seances/S01-decollage/kahoot/import-kahoot.xlsx
+++ b/2-seances/S01-decollage/kahoot/import-kahoot.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Kahoot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -507,7 +507,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Copiez les 14 lignes ci-dessous dans le modele officiel telecharge depuis Kahoot (Create &gt; Kahoot &gt; Import spreadsheet), sous sa ligne d'en-tete. La bonne reponse est indiquee par son numero (1 a 4) et apparait en vert.</t>
+          <t>Copiez les 15 lignes ci-dessous dans le modele officiel telecharge depuis Kahoot (Create &gt; Kahoot &gt; Import spreadsheet), sous sa ligne d'en-tete. La bonne reponse est indiquee par son numero (1 a 4) et apparait en vert.</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Mark Zuckerberg</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Katherine Johnson</t>
+          <t>Elon Musk</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Grace Hopper</t>
+          <t>Gitanjali Rao</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -749,27 +749,27 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Qui a ecrit le premier programme de l'histoire ?</t>
+          <t>Qui a ecrit la premiere version de Facebook dans sa chambre d'etudiant ?</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Mark Zuckerberg</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Grace Hopper</t>
+          <t>Elon Musk</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Verone Mankou</t>
+          <t>Guido van Rossum</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Guido van Rossum</t>
+          <t>Nick D'Aloisio</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -980,33 +980,66 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Katherine Johnson a calcule a la main...</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Les trajectoires des fusees de la NASA</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Le premier jeu video</t>
+          <t>A quel age Elon Musk a-t-il vendu son premier jeu video ?</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>8 ans</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>12 ans</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Le langage Python</t>
+          <t>20 ans</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Le premier telephone</t>
+          <t>30 ans</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="G17" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Charlette N'Guessan, ivoirienne, a cree un logiciel qui...</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>reconnait le visage d'une personne</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>repare les voitures</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>traduit les langues</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>fabrique des medicaments</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" s="6" t="n">
         <v>1</v>
       </c>
     </row>
